--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N87_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N87_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.63148532761361</v>
+        <v>4.002616365737211</v>
       </c>
       <c r="D2" t="n">
-        <v>82.64264313407133</v>
+        <v>13.42942950928659</v>
       </c>
       <c r="E2" t="n">
-        <v>16.63895165266072</v>
+        <v>2.703829643557366</v>
       </c>
       <c r="F2" t="n">
-        <v>22.62842910498288</v>
+        <v>3.677119729559718</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.24840196492433</v>
+        <v>3.127865319300203</v>
       </c>
       <c r="D3" t="n">
-        <v>79.4235809996988</v>
+        <v>12.90633191245105</v>
       </c>
       <c r="E3" t="n">
-        <v>16.63895165266072</v>
+        <v>2.703829643557366</v>
       </c>
       <c r="F3" t="n">
-        <v>22.62842910498288</v>
+        <v>3.677119729559718</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.0065498594632</v>
+        <v>7.63856435216277</v>
       </c>
       <c r="D4" t="n">
-        <v>46.65048117296588</v>
+        <v>7.580703190606955</v>
       </c>
       <c r="E4" t="n">
-        <v>16.63895165266072</v>
+        <v>2.703829643557366</v>
       </c>
       <c r="F4" t="n">
-        <v>22.62842910498288</v>
+        <v>3.677119729559718</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.58817684010214</v>
+        <v>8.220578736516597</v>
       </c>
       <c r="D5" t="n">
-        <v>50.2925985772149</v>
+        <v>8.172547268797421</v>
       </c>
       <c r="E5" t="n">
-        <v>16.63895165266072</v>
+        <v>2.703829643557366</v>
       </c>
       <c r="F5" t="n">
-        <v>22.62842910498288</v>
+        <v>3.677119729559718</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.05974571559291</v>
+        <v>5.372208678783848</v>
       </c>
       <c r="D6" t="n">
-        <v>32.65495540815921</v>
+        <v>5.306430253825872</v>
       </c>
       <c r="E6" t="n">
-        <v>16.63895165266072</v>
+        <v>2.703829643557366</v>
       </c>
       <c r="F6" t="n">
-        <v>22.62842910498288</v>
+        <v>3.677119729559718</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.045459392869</v>
+        <v>4.069887151341212</v>
       </c>
       <c r="D7" t="n">
-        <v>24.64328593854404</v>
+        <v>4.004533965013407</v>
       </c>
       <c r="E7" t="n">
-        <v>16.63895165266072</v>
+        <v>2.703829643557366</v>
       </c>
       <c r="F7" t="n">
-        <v>22.62842910498288</v>
+        <v>3.677119729559718</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.61887637132916</v>
+        <v>4.975567410340989</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29662196852894</v>
+        <v>4.923201069885953</v>
       </c>
       <c r="E8" t="n">
-        <v>16.63895165266072</v>
+        <v>2.703829643557366</v>
       </c>
       <c r="F8" t="n">
-        <v>22.62842910498288</v>
+        <v>3.677119729559718</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>66.38444846251724</v>
+        <v>10.78747287515905</v>
       </c>
       <c r="D9" t="n">
-        <v>66.23710941190222</v>
+        <v>10.76353027943411</v>
       </c>
       <c r="E9" t="n">
-        <v>16.63895165266072</v>
+        <v>2.703829643557366</v>
       </c>
       <c r="F9" t="n">
-        <v>22.62842910498288</v>
+        <v>3.677119729559718</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.93204892286559</v>
+        <v>4.051457949965658</v>
       </c>
       <c r="D10" t="n">
-        <v>24.73845078376418</v>
+        <v>4.01999825236168</v>
       </c>
       <c r="E10" t="n">
-        <v>16.63895165266072</v>
+        <v>2.703829643557366</v>
       </c>
       <c r="F10" t="n">
-        <v>22.62842910498288</v>
+        <v>3.677119729559718</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>7.014121465799679</v>
+        <v>1.139794738192448</v>
       </c>
       <c r="D11" t="n">
-        <v>6.82331206690117</v>
+        <v>1.10878821087144</v>
       </c>
       <c r="E11" t="n">
-        <v>16.63895165266072</v>
+        <v>2.703829643557366</v>
       </c>
       <c r="F11" t="n">
-        <v>22.62842910498288</v>
+        <v>3.677119729559718</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>9.194167411372376</v>
+        <v>1.494052204348011</v>
       </c>
       <c r="D12" t="n">
-        <v>9.624383071423091</v>
+        <v>1.563962249106252</v>
       </c>
       <c r="E12" t="n">
-        <v>16.63895165266072</v>
+        <v>2.703829643557366</v>
       </c>
       <c r="F12" t="n">
-        <v>22.62842910498288</v>
+        <v>3.677119729559718</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>45.38430902886006</v>
+        <v>7.37495021718976</v>
       </c>
       <c r="D13" t="n">
-        <v>45.44800505855864</v>
+        <v>7.38530082201578</v>
       </c>
       <c r="E13" t="n">
-        <v>16.63895165266072</v>
+        <v>2.703829643557366</v>
       </c>
       <c r="F13" t="n">
-        <v>22.62842910498288</v>
+        <v>3.677119729559718</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>14.98516915563984</v>
+        <v>2.435089987791474</v>
       </c>
       <c r="D14" t="n">
-        <v>15.38493464513555</v>
+        <v>2.500051879834527</v>
       </c>
       <c r="E14" t="n">
-        <v>16.63895165266072</v>
+        <v>2.703829643557366</v>
       </c>
       <c r="F14" t="n">
-        <v>22.62842910498288</v>
+        <v>3.677119729559718</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>36.36191351630105</v>
+        <v>5.908810946398921</v>
       </c>
       <c r="D15" t="n">
-        <v>36.71658861377638</v>
+        <v>5.966445649738662</v>
       </c>
       <c r="E15" t="n">
-        <v>16.63895165266072</v>
+        <v>2.703829643557366</v>
       </c>
       <c r="F15" t="n">
-        <v>22.62842910498288</v>
+        <v>3.677119729559718</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>53.29547007492084</v>
+        <v>8.660513887174638</v>
       </c>
       <c r="D16" t="n">
-        <v>53.59113767732436</v>
+        <v>8.708559872565209</v>
       </c>
       <c r="E16" t="n">
-        <v>16.63895165266072</v>
+        <v>2.703829643557366</v>
       </c>
       <c r="F16" t="n">
-        <v>22.62842910498288</v>
+        <v>3.677119729559718</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
